--- a/hw/kicad/bom.xlsx
+++ b/hw/kicad/bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\esl1_fpga_fir\hw\kicad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643F76E0-60C2-49E3-A6B5-D067A69A5C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785A42E5-E03E-4607-BB07-16E6DDD3E25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="26415" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
